--- a/Result/profitability/1721.xlsx
+++ b/Result/profitability/1721.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.31875</v>
+        <v>-0.33875</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.52875</v>
+        <v>-4.510000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.30125</v>
+        <v>-0.3075</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.43875</v>
+        <v>-3.4725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2875</v>
+        <v>-0.29125</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.35375</v>
+        <v>-2.695</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32</v>
+        <v>-0.2725</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.6075</v>
+        <v>-1.215</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.24125</v>
+        <v>-0.245</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0924999999999998</v>
+        <v>-0.09624999999999995</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>-0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.23125</v>
+        <v>-0.17625</v>
       </c>
       <c r="N7" t="n">
-        <v>1.38</v>
+        <v>3.59</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1375</v>
+        <v>-0.12625</v>
       </c>
       <c r="N8" t="n">
-        <v>5.38625</v>
+        <v>5.83</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.16</v>
       </c>
       <c r="N10" t="n">
-        <v>6.3275</v>
+        <v>6.327500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.16375</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3275</v>
+        <v>6.327500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>413</v>
+      </c>
+      <c r="D75" t="n">
+        <v>422</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-50</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-4.58125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2499999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6305506216696271</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5846153846153845</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8426626323751891</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
